--- a/entrepreneur_forms/033_virtual_talent_application_form--entrepreneur_forms.xlsx
+++ b/entrepreneur_forms/033_virtual_talent_application_form--entrepreneur_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'option_8',_'label':_'option_8'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'option_8', 'label': 'Option 8'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'option_9',_'label':_'option_9'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'option_9', 'label': 'Option 9'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'option_10',_'label':_'option_10'}</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'option_10', 'label': 'Option 10'}</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'option_11',_'label':_'option_11'}</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'option_11', 'label': 'Option 11'}</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'option_12',_'label':_'option_12'}</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'option_12', 'label': 'Option 12'}</t>
+          <t>Option 12</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'option_13',_'label':_'option_13'}</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'option_13', 'label': 'Option 13'}</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'option_14',_'label':_'option_14'}</t>
+          <t>option_14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'option_14', 'label': 'Option 14'}</t>
+          <t>Option 14</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'option_15',_'label':_'option_15'}</t>
+          <t>option_15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'option_15', 'label': 'Option 15'}</t>
+          <t>Option 15</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'option_16',_'label':_'option_16'}</t>
+          <t>option_16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'option_16', 'label': 'Option 16'}</t>
+          <t>Option 16</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'option_17',_'label':_'option_17'}</t>
+          <t>option_17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'option_17', 'label': 'Option 17'}</t>
+          <t>Option 17</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'option_18',_'label':_'option_18'}</t>
+          <t>option_18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'option_18', 'label': 'Option 18'}</t>
+          <t>Option 18</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'option_19',_'label':_'option_19'}</t>
+          <t>option_19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'option_19', 'label': 'Option 19'}</t>
+          <t>Option 19</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'option_20',_'label':_'option_20'}</t>
+          <t>option_20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'option_20', 'label': 'Option 20'}</t>
+          <t>Option 20</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'option_21',_'label':_'option_21'}</t>
+          <t>option_21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'option_21', 'label': 'Option 21'}</t>
+          <t>Option 21</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'option_22',_'label':_'option_22'}</t>
+          <t>option_22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'option_22', 'label': 'Option 22'}</t>
+          <t>Option 22</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'option_23',_'label':_'option_23'}</t>
+          <t>option_23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'option_23', 'label': 'Option 23'}</t>
+          <t>Option 23</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'option_24',_'label':_'option_24'}</t>
+          <t>option_24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'option_24', 'label': 'Option 24'}</t>
+          <t>Option 24</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'option_25',_'label':_'option_25'}</t>
+          <t>option_25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'option_25', 'label': 'Option 25'}</t>
+          <t>Option 25</t>
         </is>
       </c>
     </row>
